--- a/assets/constructions/examples/ctd_eths_blank.xlsx
+++ b/assets/constructions/examples/ctd_eths_blank.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,11 +504,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VDI-A2-16x40x60</t>
+          <t>VDI-A1-20x100</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -528,7 +548,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DIN_69880_1:VDI16</t>
+          <t>DIN_69880_1:VDI20</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -538,19 +558,21 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ROUND</t>
+          <t>SQUARE</t>
         </is>
       </c>
       <c r="H2" t="n">
+        <v>65</v>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="n">
         <v>60</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>40</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
@@ -561,11 +583,17 @@
           <t>2020 / KFH Website</t>
         </is>
       </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VDI-A1-20x100</t>
+          <t>VDI-A2-16x40x60</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,7 +613,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DIN_69880_1:VDI20</t>
+          <t>DIN_69880_1:VDI16</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -595,21 +623,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SQUARE</t>
+          <t>ROUND</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65</v>
-      </c>
-      <c r="I3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J3" t="n">
         <v>60</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>40</v>
+      </c>
       <c r="L3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
@@ -620,6 +646,12 @@
           <t>2020 / KFH Website</t>
         </is>
       </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
